--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -389,16 +389,6 @@
   </si>
   <si>
     <t>Code of the examination</t>
-  </si>
-  <si>
-    <t>PSSResponse.treatmentOptions.scoreValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>PSS score value</t>
   </si>
   <si>
     <t>PSSResponse.treatmentOptions.scoreRating</t>
@@ -734,7 +724,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.5546875" customWidth="true" bestFit="true"/>
@@ -2018,13 +2008,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2092,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2118,7 +2108,7 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>125</v>
@@ -2175,7 +2165,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2287,106 +2277,6 @@
         <v>73</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponse</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponse</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
